--- a/artfynd/A 6175-2022 artfynd.xlsx
+++ b/artfynd/A 6175-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6175-2022 artfynd.xlsx
+++ b/artfynd/A 6175-2022 artfynd.xlsx
@@ -1462,12 +1462,7 @@
         <v>99706365</v>
       </c>
       <c r="B9" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,16 +1488,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ekeby Mårdnäset, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552421.9239901267</v>
+        <v>552422</v>
       </c>
       <c r="R9" t="n">
-        <v>6532640.390793836</v>
+        <v>6532640</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1532,27 +1535,18 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1798,12 +1792,7 @@
         <v>99706364</v>
       </c>
       <c r="B12" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,16 +1818,25 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ekeby Mårdnäset, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552379.2651761334</v>
+        <v>552379</v>
       </c>
       <c r="R12" t="n">
-        <v>6532696.601192111</v>
+        <v>6532697</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1868,27 +1866,18 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6175-2022 artfynd.xlsx
+++ b/artfynd/A 6175-2022 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>99706365</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>99706364</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 6175-2022 artfynd.xlsx
+++ b/artfynd/A 6175-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99706354</v>
+        <v>99706353</v>
       </c>
       <c r="B2" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552454.4633524346</v>
+        <v>552461</v>
       </c>
       <c r="R2" t="n">
-        <v>6532605.726381073</v>
+        <v>6532608</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,19 +743,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99706356</v>
+        <v>99706354</v>
       </c>
       <c r="B3" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552462.9027487962</v>
+        <v>552454</v>
       </c>
       <c r="R3" t="n">
-        <v>6532631.655767264</v>
+        <v>6532605</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -860,19 +840,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99706361</v>
+        <v>99706355</v>
       </c>
       <c r="B4" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552456.2467757735</v>
+        <v>552443</v>
       </c>
       <c r="R4" t="n">
-        <v>6532588.713072114</v>
+        <v>6532604</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -972,19 +937,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99706355</v>
+        <v>99706356</v>
       </c>
       <c r="B5" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552443.1007579446</v>
+        <v>552463</v>
       </c>
       <c r="R5" t="n">
-        <v>6532604.539029089</v>
+        <v>6532632</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1084,19 +1034,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99706415</v>
+        <v>99706357</v>
       </c>
       <c r="B6" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5445</v>
+        <v>1460</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552446.5838467991</v>
+        <v>552459</v>
       </c>
       <c r="R6" t="n">
-        <v>6532652.601142811</v>
+        <v>6532635</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1196,19 +1131,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99706385</v>
+        <v>99706358</v>
       </c>
       <c r="B7" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2590</v>
+        <v>1460</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552367.1518109241</v>
+        <v>552477</v>
       </c>
       <c r="R7" t="n">
-        <v>6532636.547782643</v>
+        <v>6532605</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1308,19 +1228,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99706346</v>
+        <v>99706359</v>
       </c>
       <c r="B8" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>1460</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552452.7329654554</v>
+        <v>552457</v>
       </c>
       <c r="R8" t="n">
-        <v>6532656.815170704</v>
+        <v>6532584</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1420,19 +1325,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,53 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99706365</v>
+        <v>99706361</v>
       </c>
       <c r="B9" t="n">
-        <v>8451</v>
+        <v>75412</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>1460</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ekeby Mårdnäset, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552422</v>
+        <v>552457</v>
       </c>
       <c r="R9" t="n">
-        <v>6532640</v>
+        <v>6532588</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1546,7 +1433,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1565,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99706345</v>
+        <v>99706362</v>
       </c>
       <c r="B10" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>1460</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1605,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552394.9128312711</v>
+        <v>552472</v>
       </c>
       <c r="R10" t="n">
-        <v>6532572.905507499</v>
+        <v>6532584</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1638,19 +1519,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99706358</v>
+        <v>99706385</v>
       </c>
       <c r="B11" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1460</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1717,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552477.2307321953</v>
+        <v>552367</v>
       </c>
       <c r="R11" t="n">
-        <v>6532605.004020846</v>
+        <v>6532637</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1750,19 +1616,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,54 +1645,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>99706364</v>
+        <v>99706345</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ekeby Mårdnäset, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552379</v>
+        <v>552395</v>
       </c>
       <c r="R12" t="n">
-        <v>6532697</v>
+        <v>6532573</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1877,7 +1724,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1896,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>99706353</v>
+        <v>99706346</v>
       </c>
       <c r="B13" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1460</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552461.1577899852</v>
+        <v>552452</v>
       </c>
       <c r="R13" t="n">
-        <v>6532607.882742118</v>
+        <v>6532657</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1969,19 +1810,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>99706359</v>
+        <v>99706415</v>
       </c>
       <c r="B14" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1460</v>
+        <v>5445</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2048,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552456.3170974989</v>
+        <v>552447</v>
       </c>
       <c r="R14" t="n">
-        <v>6532583.551104874</v>
+        <v>6532652</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2081,19 +1907,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,50 +1936,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>99706357</v>
+        <v>99706364</v>
       </c>
       <c r="B15" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1460</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ekeby Mårdnäset, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552458.709550802</v>
+        <v>552379</v>
       </c>
       <c r="R15" t="n">
-        <v>6532635.728926776</v>
+        <v>6532697</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2193,27 +2013,18 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2232,50 +2043,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>99706362</v>
+        <v>99706365</v>
       </c>
       <c r="B16" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1460</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ekeby Mårdnäset, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552471.313683657</v>
+        <v>552422</v>
       </c>
       <c r="R16" t="n">
-        <v>6532583.755433243</v>
+        <v>6532640</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2305,27 +2119,18 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2344,15 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>99706423</v>
+        <v>99706396</v>
       </c>
       <c r="B17" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2384,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552490.7568760031</v>
+        <v>552368</v>
       </c>
       <c r="R17" t="n">
-        <v>6532561.30347683</v>
+        <v>6532617</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2417,19 +2217,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2456,15 +2246,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>99706425</v>
+        <v>99706397</v>
       </c>
       <c r="B18" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2472,21 +2257,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2496,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552343.3342332278</v>
+        <v>552343</v>
       </c>
       <c r="R18" t="n">
-        <v>6532676.493981261</v>
+        <v>6532678</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2529,19 +2314,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2568,15 +2343,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>99706427</v>
+        <v>99706398</v>
       </c>
       <c r="B19" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,21 +2354,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2378,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552404.5992251298</v>
+        <v>552376</v>
       </c>
       <c r="R19" t="n">
-        <v>6532659.25746779</v>
+        <v>6532715</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2641,19 +2411,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,15 +2440,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>99706426</v>
+        <v>99706422</v>
       </c>
       <c r="B20" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2720,10 +2475,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552354.2895616286</v>
+        <v>552454</v>
       </c>
       <c r="R20" t="n">
-        <v>6532707.619601013</v>
+        <v>6532588</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2753,19 +2508,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2792,15 +2537,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>99706424</v>
+        <v>99706423</v>
       </c>
       <c r="B21" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,10 +2572,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552392.6827870293</v>
+        <v>552491</v>
       </c>
       <c r="R21" t="n">
-        <v>6532584.749908051</v>
+        <v>6532561</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2865,19 +2605,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2904,15 +2634,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>99706428</v>
+        <v>99706424</v>
       </c>
       <c r="B22" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,10 +2669,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552446.513537659</v>
+        <v>552392</v>
       </c>
       <c r="R22" t="n">
-        <v>6532657.763017749</v>
+        <v>6532585</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2977,19 +2702,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3016,15 +2731,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>99706422</v>
+        <v>99706425</v>
       </c>
       <c r="B23" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3056,10 +2766,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552454.6954068425</v>
+        <v>552344</v>
       </c>
       <c r="R23" t="n">
-        <v>6532588.691938047</v>
+        <v>6532676</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3089,19 +2799,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,15 +2828,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>99706398</v>
+        <v>99706426</v>
       </c>
       <c r="B24" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,21 +2839,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3168,10 +2863,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552375.9167731785</v>
+        <v>552354</v>
       </c>
       <c r="R24" t="n">
-        <v>6532714.625311189</v>
+        <v>6532707</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3201,19 +2896,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3240,15 +2925,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>99706397</v>
+        <v>99706427</v>
       </c>
       <c r="B25" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3256,21 +2936,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3280,10 +2960,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552342.278960148</v>
+        <v>552405</v>
       </c>
       <c r="R25" t="n">
-        <v>6532678.028475457</v>
+        <v>6532659</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3313,19 +2993,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3352,15 +3022,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>99706396</v>
+        <v>99706428</v>
       </c>
       <c r="B26" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,21 +3033,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3392,10 +3057,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552367.9427206144</v>
+        <v>552447</v>
       </c>
       <c r="R26" t="n">
-        <v>6532616.423355811</v>
+        <v>6532658</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3425,19 +3090,9 @@
           <t>2022-04-06</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,6 +3116,103 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>99706429</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ekeby Mårdnäset, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>552493</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6532678</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-04-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-04-06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6175-2022 artfynd.xlsx
+++ b/artfynd/A 6175-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706353</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706354</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706355</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706356</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706357</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706358</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706359</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706361</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706362</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706385</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706345</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706346</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706415</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706364</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2146,6 +2221,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706365</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2243,6 +2323,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706396</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2340,6 +2425,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706397</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2437,6 +2527,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706398</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2534,6 +2629,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706422</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2631,6 +2731,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706423</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2728,6 +2833,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706424</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2825,6 +2935,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706425</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2922,6 +3037,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706426</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3019,6 +3139,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706427</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3116,6 +3241,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706428</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3213,8 +3343,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99706429</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>